--- a/build/rooms.xlsx
+++ b/build/rooms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>RoomNumber</t>
   </si>
@@ -34,28 +34,49 @@
     <t>Floor</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>100.00</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>lyheng</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>150.00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>500.00</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t/>
+    <t>103</t>
+  </si>
+  <si>
+    <t>200.00</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>1000.00</t>
-  </si>
-  <si>
-    <t>korea</t>
+    <t>104</t>
+  </si>
+  <si>
+    <t>250.00</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -365,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -405,27 +426,67 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
